--- a/public/downloads/BothraExtendedICOHP2024.xlsx
+++ b/public/downloads/BothraExtendedICOHP2024.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>OH</t>
@@ -656,10 +679,10 @@
         <v>185</v>
       </c>
       <c r="N3" s="5">
-        <v>2118.779312610626</v>
+        <v>2118779.312610626</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03208813134348972</v>
+        <v>32.08813134348972</v>
       </c>
       <c r="P3" s="5">
         <v>66030</v>
@@ -706,10 +729,10 @@
         <v>185</v>
       </c>
       <c r="N4" s="5">
-        <v>1300.032502651215</v>
+        <v>1300032.502651215</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04365455012260627</v>
+        <v>43.65455012260627</v>
       </c>
       <c r="P4" s="5">
         <v>29780</v>
@@ -756,10 +779,10 @@
         <v>185</v>
       </c>
       <c r="N5" s="5">
-        <v>4127.399039745331</v>
+        <v>4127399.039745331</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1239645304023226</v>
+        <v>123.9645304023226</v>
       </c>
       <c r="P5" s="5">
         <v>33295</v>
@@ -806,10 +829,10 @@
         <v>185</v>
       </c>
       <c r="N6" s="5">
-        <v>3513.624372243881</v>
+        <v>3513624.372243881</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08513955686456859</v>
+        <v>85.13955686456859</v>
       </c>
       <c r="P6" s="5">
         <v>41269</v>
@@ -856,10 +879,10 @@
         <v>185</v>
       </c>
       <c r="N7" s="5">
-        <v>4225.80131149292</v>
+        <v>4225801.31149292</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1655748496000674</v>
+        <v>165.5748496000674</v>
       </c>
       <c r="P7" s="5">
         <v>25522</v>
@@ -906,10 +929,10 @@
         <v>185</v>
       </c>
       <c r="N8" s="5">
-        <v>551.4182388782501</v>
+        <v>551418.2388782501</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01188170912707126</v>
+        <v>11.88170912707126</v>
       </c>
       <c r="P8" s="5">
         <v>46409</v>
@@ -956,10 +979,10 @@
         <v>185</v>
       </c>
       <c r="N9" s="5">
-        <v>1238.013573169708</v>
+        <v>1238013.573169708</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03186076056231073</v>
+        <v>31.86076056231073</v>
       </c>
       <c r="P9" s="5">
         <v>38857</v>
@@ -1006,10 +1029,10 @@
         <v>185</v>
       </c>
       <c r="N10" s="5">
-        <v>4192.772398471832</v>
+        <v>4192772.398471832</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08756468815988956</v>
+        <v>87.56468815988956</v>
       </c>
       <c r="P10" s="5">
         <v>47882</v>
@@ -1056,10 +1079,10 @@
         <v>185</v>
       </c>
       <c r="N11" s="5">
-        <v>1870.220494747162</v>
+        <v>1870220.494747162</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04463000822687416</v>
+        <v>44.63000822687417</v>
       </c>
       <c r="P11" s="5">
         <v>41905</v>
@@ -1106,10 +1129,10 @@
         <v>185</v>
       </c>
       <c r="N12" s="5">
-        <v>384.8472802639008</v>
+        <v>384847.2802639008</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01898511569552073</v>
+        <v>18.98511569552073</v>
       </c>
       <c r="P12" s="5">
         <v>20271</v>
@@ -1156,10 +1179,10 @@
         <v>185</v>
       </c>
       <c r="N13" s="5">
-        <v>4301.67143201828</v>
+        <v>4301671.43201828</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07778228395809128</v>
+        <v>77.78228395809128</v>
       </c>
       <c r="P13" s="5">
         <v>55304</v>
@@ -1206,10 +1229,10 @@
         <v>185</v>
       </c>
       <c r="N14" s="5">
-        <v>13499.07896661758</v>
+        <v>13499078.96661758</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2397321736599404</v>
+        <v>239.7321736599404</v>
       </c>
       <c r="P14" s="5">
         <v>56309</v>
@@ -1256,10 +1279,10 @@
         <v>185</v>
       </c>
       <c r="N15" s="5">
-        <v>5528.080529689789</v>
+        <v>5528080.529689789</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2376442494063188</v>
+        <v>237.6442494063188</v>
       </c>
       <c r="P15" s="5">
         <v>23262</v>
@@ -1306,10 +1329,10 @@
         <v>185</v>
       </c>
       <c r="N16" s="5">
-        <v>8451.921570777893</v>
+        <v>8451921.570777893</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09897095448111072</v>
+        <v>98.97095448111072</v>
       </c>
       <c r="P16" s="5">
         <v>85398</v>
@@ -1356,10 +1379,10 @@
         <v>185</v>
       </c>
       <c r="N17" s="5">
-        <v>2665.826070785522</v>
+        <v>2665826.070785522</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1010050418969243</v>
+        <v>101.0050418969243</v>
       </c>
       <c r="P17" s="5">
         <v>26393</v>
@@ -1387,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1398,9 +1421,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1434,8 +1463,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1457,91 +1494,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2741765123838625</v>
+        <v>0.3178805346572751</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1672513269804764</v>
+        <v>0.2039623501230684</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1548991248220433</v>
+        <v>0.2128451672061387</v>
       </c>
       <c r="E3" s="4">
-        <v>79.38884064263991</v>
+        <v>77.31364886380055</v>
       </c>
       <c r="F3" s="4">
-        <v>84.35170641153898</v>
+        <v>80.5345328192676</v>
       </c>
       <c r="G3" s="5">
         <v>94</v>
       </c>
       <c r="H3" s="5">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J3" s="5">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.0128715771693644</v>
+      </c>
+      <c r="O3" s="5">
+        <v>74</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3183905413976887</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2039144355949794</v>
+      </c>
+      <c r="R3" s="5">
+        <v>74</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3358157374893913</v>
+        <v>0.323340878702245</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2050177562296358</v>
+        <v>0.2763823921008396</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1812642412274499</v>
+        <v>0.248522418847871</v>
       </c>
       <c r="E4" s="4">
-        <v>82.93488824101115</v>
+        <v>81.1930926216645</v>
       </c>
       <c r="F4" s="4">
-        <v>87.38095238095175</v>
+        <v>85.16655603903912</v>
       </c>
       <c r="G4" s="5">
         <v>91</v>
       </c>
       <c r="H4" s="5">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K4" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.05405497786027094</v>
+      </c>
+      <c r="O4" s="5">
+        <v>77</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3245007575473345</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2757063815536988</v>
+      </c>
+      <c r="R4" s="5">
+        <v>77</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1552,6 +1643,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1559,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1570,9 +1662,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1606,8 +1704,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1629,91 +1735,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2759901460245601</v>
+        <v>0.4671728057005042</v>
       </c>
       <c r="C3" s="4">
-        <v>0.197741982429443</v>
+        <v>0.3064880808598545</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2092057330902761</v>
+        <v>0.2959700072024354</v>
       </c>
       <c r="E3" s="4">
-        <v>79.44782168186423</v>
+        <v>67.6555941525545</v>
       </c>
       <c r="F3" s="4">
-        <v>81.44200104717089</v>
+        <v>73.40961016707139</v>
       </c>
       <c r="G3" s="5">
         <v>94</v>
       </c>
       <c r="H3" s="5">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J3" s="5">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.07589145981201662</v>
+      </c>
+      <c r="O3" s="5">
+        <v>64</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4568039540887596</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2883660085741433</v>
+      </c>
+      <c r="R3" s="5">
+        <v>64</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4467716317846693</v>
+        <v>0.5205905138520734</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2460987505314372</v>
+        <v>0.4169578796277298</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2358216744787478</v>
+        <v>0.4311773345409519</v>
       </c>
       <c r="E4" s="4">
-        <v>80.86977648202107</v>
+        <v>69.5204455408538</v>
       </c>
       <c r="F4" s="4">
-        <v>83.94879170046849</v>
+        <v>76.00904688153028</v>
       </c>
       <c r="G4" s="5">
         <v>91</v>
       </c>
       <c r="H4" s="5">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K4" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.2919753643087848</v>
+      </c>
+      <c r="O4" s="5">
+        <v>64</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4620500737694364</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3474234947683748</v>
+      </c>
+      <c r="R4" s="5">
+        <v>64</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1724,6 +1884,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1731,7 +1892,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1742,9 +1903,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1778,8 +1945,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1801,91 +1976,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2092039350486206</v>
+        <v>0.2741765123838625</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1598674908996453</v>
+        <v>0.1672513269804764</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1675550783283646</v>
+        <v>0.1548991248220433</v>
       </c>
       <c r="E3" s="4">
-        <v>86.17057461282367</v>
+        <v>79.38884064263991</v>
       </c>
       <c r="F3" s="4">
-        <v>88.80491694035838</v>
+        <v>84.35170641153898</v>
       </c>
       <c r="G3" s="5">
         <v>94</v>
       </c>
       <c r="H3" s="5">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
+        <v>16</v>
+      </c>
+      <c r="K3" s="5">
         <v>5</v>
       </c>
-      <c r="K3" s="5">
-        <v>3</v>
-      </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.01676470390487029</v>
+      </c>
+      <c r="O3" s="5">
+        <v>77</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2737031875391309</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1686330126913733</v>
+      </c>
+      <c r="R3" s="5">
+        <v>77</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2233955061456087</v>
+        <v>0.3358157374893913</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2077416464131245</v>
+        <v>0.2050177562296358</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2015227975760317</v>
+        <v>0.1812642412274499</v>
       </c>
       <c r="E4" s="4">
-        <v>88.49517829109689</v>
+        <v>82.93488824101115</v>
       </c>
       <c r="F4" s="4">
-        <v>90.77832681859422</v>
+        <v>87.38095238095175</v>
       </c>
       <c r="G4" s="5">
         <v>91</v>
       </c>
       <c r="H4" s="5">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.04699040926869867</v>
+      </c>
+      <c r="O4" s="5">
+        <v>74</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3352925139609041</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2011993050480707</v>
+      </c>
+      <c r="R4" s="5">
+        <v>74</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1896,6 +2125,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1903,7 +2133,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1914,9 +2144,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1950,8 +2186,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1973,25 +2217,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3361930756375162</v>
+        <v>0.2759901460245601</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2278964164540981</v>
+        <v>0.197741982429443</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2282747902386193</v>
+        <v>0.2092057330902761</v>
       </c>
       <c r="E3" s="4">
-        <v>77.74895064408726</v>
+        <v>79.44782168186423</v>
       </c>
       <c r="F3" s="4">
-        <v>82.03900709219882</v>
+        <v>81.44200104717089</v>
       </c>
       <c r="G3" s="5">
         <v>94</v>
@@ -2000,64 +2262,100 @@
         <v>80</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.03376189849194864</v>
+      </c>
+      <c r="O3" s="5">
+        <v>80</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2730668598281666</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1951511686109794</v>
+      </c>
+      <c r="R3" s="5">
+        <v>80</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3176388725032462</v>
+        <v>0.4467716317846693</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2196390093658454</v>
+        <v>0.2460987505314372</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2079299485034589</v>
+        <v>0.2358216744787478</v>
       </c>
       <c r="E4" s="4">
-        <v>80.45451147491956</v>
+        <v>80.86977648202107</v>
       </c>
       <c r="F4" s="4">
-        <v>85.52412911473144</v>
+        <v>83.94879170046849</v>
       </c>
       <c r="G4" s="5">
         <v>91</v>
       </c>
       <c r="H4" s="5">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L4" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.117955163104485</v>
+      </c>
+      <c r="O4" s="5">
+        <v>74</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4489634952503799</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2374027136852435</v>
+      </c>
+      <c r="R4" s="5">
+        <v>74</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2068,6 +2366,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2075,7 +2374,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2086,9 +2385,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2122,8 +2427,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2145,91 +2458,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4957180663518998</v>
+        <v>0.2092039350486206</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2504370834885079</v>
+        <v>0.1598674908996453</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3012297450608433</v>
+        <v>0.1675550783283646</v>
       </c>
       <c r="E3" s="4">
-        <v>63.99840787378791</v>
+        <v>86.17057461282367</v>
       </c>
       <c r="F3" s="4">
-        <v>74.74403826931318</v>
+        <v>88.80491694035838</v>
       </c>
       <c r="G3" s="5">
         <v>94</v>
       </c>
       <c r="H3" s="5">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.05440567682134034</v>
+      </c>
+      <c r="O3" s="5">
+        <v>89</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2000756801303786</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1496151129318241</v>
+      </c>
+      <c r="R3" s="5">
+        <v>89</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.812748708972164</v>
+        <v>0.2233955061456087</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4713640287487284</v>
+        <v>0.2077416464131245</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5844310649611568</v>
+        <v>0.2015227975760317</v>
       </c>
       <c r="E4" s="4">
-        <v>64.03715332286777</v>
+        <v>88.49517829109689</v>
       </c>
       <c r="F4" s="4">
-        <v>73.39073677999922</v>
+        <v>90.77832681859422</v>
       </c>
       <c r="G4" s="5">
         <v>91</v>
       </c>
       <c r="H4" s="5">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
         <v>3</v>
       </c>
-      <c r="J4" s="5">
-        <v>27</v>
-      </c>
       <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
         <v>3</v>
       </c>
-      <c r="L4" s="5">
-        <v>24</v>
-      </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.0131191042704746</v>
+      </c>
+      <c r="O4" s="5">
+        <v>87</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.225860254331095</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2103197163542654</v>
+      </c>
+      <c r="R4" s="5">
+        <v>87</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2240,6 +2607,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2247,7 +2615,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2258,9 +2626,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2294,8 +2668,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2317,91 +2699,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4329319103391446</v>
+        <v>0.3361930756375162</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3923485846535208</v>
+        <v>0.2278964164540981</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3868327575962073</v>
+        <v>0.2282747902386193</v>
       </c>
       <c r="E3" s="4">
-        <v>89.5722970039082</v>
+        <v>77.74895064408726</v>
       </c>
       <c r="F3" s="4">
-        <v>91.56992241420323</v>
+        <v>82.03900709219882</v>
       </c>
       <c r="G3" s="5">
         <v>94</v>
       </c>
       <c r="H3" s="5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1795598035314893</v>
+      </c>
+      <c r="O3" s="5">
+        <v>80</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2677656617853166</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1592812552019645</v>
+      </c>
+      <c r="R3" s="5">
+        <v>80</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3493179445324497</v>
+        <v>0.3176388725032462</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2947593513608645</v>
+        <v>0.2196390093658454</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2914037152418562</v>
+        <v>0.2079299485034589</v>
       </c>
       <c r="E4" s="4">
-        <v>90.30836510428404</v>
+        <v>80.45451147491956</v>
       </c>
       <c r="F4" s="4">
-        <v>91.6570789389578</v>
+        <v>85.52412911473144</v>
       </c>
       <c r="G4" s="5">
         <v>91</v>
       </c>
       <c r="H4" s="5">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K4" s="5">
         <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.0653595971840879</v>
+      </c>
+      <c r="O4" s="5">
+        <v>80</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.320612133806489</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2233522430463858</v>
+      </c>
+      <c r="R4" s="5">
+        <v>80</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2412,6 +2848,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2419,7 +2856,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2430,9 +2867,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2466,8 +2909,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2489,91 +2940,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7058101036426375</v>
+        <v>0.4957180663518998</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4159426333806918</v>
+        <v>0.2504370834885079</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4446074732638012</v>
+        <v>0.3012297450608433</v>
       </c>
       <c r="E3" s="4">
-        <v>50.52395426255597</v>
+        <v>63.99840787378791</v>
       </c>
       <c r="F3" s="4">
-        <v>61.57896615736109</v>
+        <v>74.74403826931318</v>
       </c>
       <c r="G3" s="5">
         <v>94</v>
       </c>
       <c r="H3" s="5">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>25</v>
+      </c>
+      <c r="K3" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="5">
-        <v>42</v>
-      </c>
-      <c r="K3" s="5">
-        <v>6</v>
-      </c>
       <c r="L3" s="5">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1755645989607876</v>
+      </c>
+      <c r="O3" s="5">
+        <v>69</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4393403106561931</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1507328744154132</v>
+      </c>
+      <c r="R3" s="5">
+        <v>69</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.08614059375366</v>
+        <v>0.812748708972164</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5422497861355664</v>
+        <v>0.4713640287487284</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6616910060626578</v>
+        <v>0.5844310649611568</v>
       </c>
       <c r="E4" s="4">
-        <v>49.64977199671088</v>
+        <v>64.03715332286777</v>
       </c>
       <c r="F4" s="4">
-        <v>59.41256729847349</v>
+        <v>73.39073677999922</v>
       </c>
       <c r="G4" s="5">
         <v>91</v>
       </c>
       <c r="H4" s="5">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="I4" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="K4" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.3364760903101248</v>
+      </c>
+      <c r="O4" s="5">
+        <v>61</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7578558374710435</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2778677128712014</v>
+      </c>
+      <c r="R4" s="5">
+        <v>60</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2584,6 +3089,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2591,7 +3097,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2602,9 +3108,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2638,8 +3150,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2661,66 +3181,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3274673334635874</v>
+        <v>0.4329319103391446</v>
       </c>
       <c r="C3" s="4">
-        <v>0.252583985561407</v>
+        <v>0.3923485846535208</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2588763557730815</v>
+        <v>0.3868327575962073</v>
       </c>
       <c r="E3" s="4">
-        <v>86.44992039368883</v>
+        <v>89.5722970039082</v>
       </c>
       <c r="F3" s="4">
-        <v>88.83704602789409</v>
+        <v>91.56992241420323</v>
       </c>
       <c r="G3" s="5">
         <v>94</v>
       </c>
       <c r="H3" s="5">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I3" s="5">
         <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3799980288902891</v>
+      </c>
+      <c r="O3" s="5">
+        <v>85</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1643812198647925</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09947329699392547</v>
+      </c>
+      <c r="R3" s="5">
+        <v>85</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3453750398456961</v>
+        <v>0.3493179445324497</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2885592551311042</v>
+        <v>0.2947593513608645</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2787834466854737</v>
+        <v>0.2914037152418562</v>
       </c>
       <c r="E4" s="4">
-        <v>87.91844210211508</v>
+        <v>90.30836510428404</v>
       </c>
       <c r="F4" s="4">
-        <v>89.63369963370005</v>
+        <v>91.6570789389578</v>
       </c>
       <c r="G4" s="5">
         <v>91</v>
@@ -2735,17 +3291,35 @@
         <v>8</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.2186939960312101</v>
+      </c>
+      <c r="O4" s="5">
+        <v>82</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2249649526870856</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1659009045009317</v>
+      </c>
+      <c r="R4" s="5">
+        <v>82</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2756,12 +3330,1352 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.7058101036426375</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4159426333806918</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4446074732638012</v>
+      </c>
+      <c r="E3" s="4">
+        <v>50.52395426255597</v>
+      </c>
+      <c r="F3" s="4">
+        <v>61.57896615736109</v>
+      </c>
+      <c r="G3" s="5">
+        <v>94</v>
+      </c>
+      <c r="H3" s="5">
+        <v>49</v>
+      </c>
+      <c r="I3" s="5">
+        <v>3</v>
+      </c>
+      <c r="J3" s="5">
+        <v>42</v>
+      </c>
+      <c r="K3" s="5">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5">
+        <v>36</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.3541591323731986</v>
+      </c>
+      <c r="O3" s="5">
+        <v>49</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6119827170718913</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2170270575513353</v>
+      </c>
+      <c r="R3" s="5">
+        <v>49</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.08614059375366</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5422497861355664</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.6616910060626578</v>
+      </c>
+      <c r="E4" s="4">
+        <v>49.64977199671088</v>
+      </c>
+      <c r="F4" s="4">
+        <v>59.41256729847349</v>
+      </c>
+      <c r="G4" s="5">
+        <v>91</v>
+      </c>
+      <c r="H4" s="5">
+        <v>38</v>
+      </c>
+      <c r="I4" s="5">
+        <v>6</v>
+      </c>
+      <c r="J4" s="5">
+        <v>47</v>
+      </c>
+      <c r="K4" s="5">
+        <v>8</v>
+      </c>
+      <c r="L4" s="5">
+        <v>39</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.259357368629606</v>
+      </c>
+      <c r="O4" s="5">
+        <v>38</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.046046642690524</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3956478893497778</v>
+      </c>
+      <c r="R4" s="5">
+        <v>38</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.3274673334635874</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.252583985561407</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2588763557730815</v>
+      </c>
+      <c r="E3" s="4">
+        <v>86.44992039368883</v>
+      </c>
+      <c r="F3" s="4">
+        <v>88.83704602789409</v>
+      </c>
+      <c r="G3" s="5">
+        <v>94</v>
+      </c>
+      <c r="H3" s="5">
+        <v>83</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>9</v>
+      </c>
+      <c r="K3" s="5">
+        <v>3</v>
+      </c>
+      <c r="L3" s="5">
+        <v>6</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2280357003599367</v>
+      </c>
+      <c r="O3" s="5">
+        <v>83</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1938337337137283</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1116429356729935</v>
+      </c>
+      <c r="R3" s="5">
+        <v>83</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3453750398456961</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2885592551311042</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2787834466854737</v>
+      </c>
+      <c r="E4" s="4">
+        <v>87.91844210211508</v>
+      </c>
+      <c r="F4" s="4">
+        <v>89.63369963370005</v>
+      </c>
+      <c r="G4" s="5">
+        <v>91</v>
+      </c>
+      <c r="H4" s="5">
+        <v>82</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>8</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2012602623284877</v>
+      </c>
+      <c r="O4" s="5">
+        <v>82</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2404786011029039</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1844217598390109</v>
+      </c>
+      <c r="R4" s="5">
+        <v>82</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>76.75675675675676</v>
+      </c>
+      <c r="C3" s="3">
+        <v>4.324324324324325</v>
+      </c>
+      <c r="D3" s="3">
+        <v>18.91891891891892</v>
+      </c>
+      <c r="E3" s="3">
+        <v>5.945945945945946</v>
+      </c>
+      <c r="F3" s="3">
+        <v>12.97297297297297</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4714477193262163</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2532742736321817</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.227121294426946</v>
+      </c>
+      <c r="K3" s="4">
+        <v>72.54624011766875</v>
+      </c>
+      <c r="L3" s="4">
+        <v>78.6215611584734</v>
+      </c>
+      <c r="M3" s="5">
+        <v>185</v>
+      </c>
+      <c r="N3" s="5">
+        <v>2118779.312610626</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.08813134348972</v>
+      </c>
+      <c r="P3" s="5">
+        <v>66030</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>85.94594594594595</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="D4" s="3">
+        <v>11.35135135135135</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2.162162162162162</v>
+      </c>
+      <c r="F4" s="3">
+        <v>9.189189189189189</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.336614280825472</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2878885545869708</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2787546311755784</v>
+      </c>
+      <c r="K4" s="4">
+        <v>76.56315499172628</v>
+      </c>
+      <c r="L4" s="4">
+        <v>81.36809964326707</v>
+      </c>
+      <c r="M4" s="5">
+        <v>185</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1300032.502651215</v>
+      </c>
+      <c r="O4" s="4">
+        <v>43.65455012260627</v>
+      </c>
+      <c r="P4" s="5">
+        <v>29780</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>86.48648648648648</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1.621621621621622</v>
+      </c>
+      <c r="D5" s="3">
+        <v>11.89189189189189</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3.243243243243243</v>
+      </c>
+      <c r="F5" s="3">
+        <v>8.648648648648649</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.2498562577964954</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1876231406196898</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2006485138323065</v>
+      </c>
+      <c r="K5" s="4">
+        <v>81.82404853833467</v>
+      </c>
+      <c r="L5" s="4">
+        <v>85.50686256726433</v>
+      </c>
+      <c r="M5" s="5">
+        <v>185</v>
+      </c>
+      <c r="N5" s="5">
+        <v>4127399.039745331</v>
+      </c>
+      <c r="O5" s="4">
+        <v>123.9645304023226</v>
+      </c>
+      <c r="P5" s="5">
+        <v>33295</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>81.62162162162161</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2.162162162162162</v>
+      </c>
+      <c r="D6" s="3">
+        <v>16.21621621621622</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3.243243243243243</v>
+      </c>
+      <c r="F6" s="3">
+        <v>12.97297297297297</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.3393378168390205</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2314893617287718</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2236576443083025</v>
+      </c>
+      <c r="K6" s="4">
+        <v>76.74793160507436</v>
+      </c>
+      <c r="L6" s="4">
+        <v>81.9210955922368</v>
+      </c>
+      <c r="M6" s="5">
+        <v>185</v>
+      </c>
+      <c r="N6" s="5">
+        <v>3513624.372243881</v>
+      </c>
+      <c r="O6" s="4">
+        <v>85.13955686456859</v>
+      </c>
+      <c r="P6" s="5">
+        <v>41269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>90.27027027027027</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2.162162162162162</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7.567567567567568</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1.621621621621622</v>
+      </c>
+      <c r="F7" s="3">
+        <v>5.945945945945946</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.1811810435180082</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1331504383001452</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1392259367113816</v>
+      </c>
+      <c r="K7" s="4">
+        <v>87.69277440705994</v>
+      </c>
+      <c r="L7" s="4">
+        <v>90.16615272991125</v>
+      </c>
+      <c r="M7" s="5">
+        <v>185</v>
+      </c>
+      <c r="N7" s="5">
+        <v>4225801.31149292</v>
+      </c>
+      <c r="O7" s="4">
+        <v>165.5748496000674</v>
+      </c>
+      <c r="P7" s="5">
+        <v>25522</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>81.62162162162161</v>
+      </c>
+      <c r="C8" s="3">
+        <v>4.324324324324325</v>
+      </c>
+      <c r="D8" s="3">
+        <v>14.05405405405405</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1.621621621621622</v>
+      </c>
+      <c r="F8" s="3">
+        <v>12.43243243243243</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.3213961071794064</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2405235736004191</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.2266087230501719</v>
+      </c>
+      <c r="K8" s="4">
+        <v>79.22191579334412</v>
+      </c>
+      <c r="L8" s="4">
+        <v>82.81298748412857</v>
+      </c>
+      <c r="M8" s="5">
+        <v>185</v>
+      </c>
+      <c r="N8" s="5">
+        <v>551418.2388782501</v>
+      </c>
+      <c r="O8" s="4">
+        <v>11.88170912707126</v>
+      </c>
+      <c r="P8" s="5">
+        <v>46409</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>69.18918918918919</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4.864864864864865</v>
+      </c>
+      <c r="D9" s="3">
+        <v>25.94594594594595</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1.621621621621622</v>
+      </c>
+      <c r="F9" s="3">
+        <v>24.32432432432433</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.4593844778235791</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.317894751671259</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.3010122220021558</v>
+      </c>
+      <c r="K9" s="4">
+        <v>68.57289943004238</v>
+      </c>
+      <c r="L9" s="4">
+        <v>74.68825201039986</v>
+      </c>
+      <c r="M9" s="5">
+        <v>185</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1238013.573169708</v>
+      </c>
+      <c r="O9" s="4">
+        <v>31.86076056231073</v>
+      </c>
+      <c r="P9" s="5">
+        <v>38857</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>81.62162162162161</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2.162162162162162</v>
+      </c>
+      <c r="D10" s="3">
+        <v>16.21621621621622</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5.405405405405405</v>
+      </c>
+      <c r="F10" s="3">
+        <v>10.81081081081081</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.3039984778330841</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1845926526542581</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1669961765068811</v>
+      </c>
+      <c r="K10" s="4">
+        <v>81.13311270454138</v>
+      </c>
+      <c r="L10" s="4">
+        <v>85.84176794243918</v>
+      </c>
+      <c r="M10" s="5">
+        <v>185</v>
+      </c>
+      <c r="N10" s="5">
+        <v>4192772.398471832</v>
+      </c>
+      <c r="O10" s="4">
+        <v>87.56468815988956</v>
+      </c>
+      <c r="P10" s="5">
+        <v>47882</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>83.24324324324324</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2.162162162162162</v>
+      </c>
+      <c r="D11" s="3">
+        <v>14.59459459459459</v>
+      </c>
+      <c r="E11" s="3">
+        <v>5.405405405405405</v>
+      </c>
+      <c r="F11" s="3">
+        <v>9.189189189189189</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.3595889886034175</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.2154538591012102</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2130428392098363</v>
+      </c>
+      <c r="K11" s="4">
+        <v>80.14726971869794</v>
+      </c>
+      <c r="L11" s="4">
+        <v>82.67507104419867</v>
+      </c>
+      <c r="M11" s="5">
+        <v>185</v>
+      </c>
+      <c r="N11" s="5">
+        <v>1870220.494747162</v>
+      </c>
+      <c r="O11" s="4">
+        <v>44.63000822687417</v>
+      </c>
+      <c r="P11" s="5">
+        <v>41905</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>95.13513513513514</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.5405405405405406</v>
+      </c>
+      <c r="D12" s="3">
+        <v>4.324324324324325</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1.621621621621622</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2127589031155959</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1796225021235991</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1811562158423017</v>
+      </c>
+      <c r="K12" s="4">
+        <v>87.31402831402767</v>
+      </c>
+      <c r="L12" s="4">
+        <v>89.77562125884101</v>
+      </c>
+      <c r="M12" s="5">
+        <v>185</v>
+      </c>
+      <c r="N12" s="5">
+        <v>384847.2802639008</v>
+      </c>
+      <c r="O12" s="4">
+        <v>18.98511569552073</v>
+      </c>
+      <c r="P12" s="5">
+        <v>20271</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>86.48648648648648</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1.621621621621622</v>
+      </c>
+      <c r="D13" s="3">
+        <v>11.89189189189189</v>
+      </c>
+      <c r="E13" s="3">
+        <v>4.324324324324325</v>
+      </c>
+      <c r="F13" s="3">
+        <v>7.567567567567568</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.293760412887623</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1913167491241752</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1799984476468247</v>
+      </c>
+      <c r="K13" s="4">
+        <v>79.07979407979391</v>
+      </c>
+      <c r="L13" s="4">
+        <v>83.75331035733701</v>
+      </c>
+      <c r="M13" s="5">
+        <v>185</v>
+      </c>
+      <c r="N13" s="5">
+        <v>4301671.43201828</v>
+      </c>
+      <c r="O13" s="4">
+        <v>77.78228395809128</v>
+      </c>
+      <c r="P13" s="5">
+        <v>55304</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>69.72972972972973</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1.621621621621622</v>
+      </c>
+      <c r="D14" s="3">
+        <v>28.64864864864865</v>
+      </c>
+      <c r="E14" s="3">
+        <v>3.243243243243243</v>
+      </c>
+      <c r="F14" s="3">
+        <v>24.86486486486487</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.5405405405405406</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.5960155157380923</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.2098653574181054</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.3317530713663741</v>
+      </c>
+      <c r="K14" s="4">
+        <v>64.01746644603791</v>
+      </c>
+      <c r="L14" s="4">
+        <v>74.07836023943486</v>
+      </c>
+      <c r="M14" s="5">
+        <v>185</v>
+      </c>
+      <c r="N14" s="5">
+        <v>13499078.96661758</v>
+      </c>
+      <c r="O14" s="4">
+        <v>239.7321736599404</v>
+      </c>
+      <c r="P14" s="5">
+        <v>56309</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>90.27027027027027</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1.621621621621622</v>
+      </c>
+      <c r="D15" s="3">
+        <v>8.108108108108109</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="F15" s="3">
+        <v>5.405405405405405</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1941818668206231</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1320904455901801</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.1357641601218892</v>
+      </c>
+      <c r="K15" s="4">
+        <v>89.93436293436262</v>
+      </c>
+      <c r="L15" s="4">
+        <v>91.61279400205562</v>
+      </c>
+      <c r="M15" s="5">
+        <v>185</v>
+      </c>
+      <c r="N15" s="5">
+        <v>5528080.529689789</v>
+      </c>
+      <c r="O15" s="4">
+        <v>237.6442494063188</v>
+      </c>
+      <c r="P15" s="5">
+        <v>23262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>47.02702702702703</v>
+      </c>
+      <c r="C16" s="3">
+        <v>4.864864864864865</v>
+      </c>
+      <c r="D16" s="3">
+        <v>48.10810810810811</v>
+      </c>
+      <c r="E16" s="3">
+        <v>7.567567567567568</v>
+      </c>
+      <c r="F16" s="3">
+        <v>40.54054054054054</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.8254952426464617</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.2950453519000804</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.4165033535760633</v>
+      </c>
+      <c r="K16" s="4">
+        <v>50.09395109395107</v>
+      </c>
+      <c r="L16" s="4">
+        <v>60.51333212407057</v>
+      </c>
+      <c r="M16" s="5">
+        <v>185</v>
+      </c>
+      <c r="N16" s="5">
+        <v>8451921.570777893</v>
+      </c>
+      <c r="O16" s="4">
+        <v>98.97095448111072</v>
+      </c>
+      <c r="P16" s="5">
+        <v>85398</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>89.18918918918919</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1.621621621621622</v>
+      </c>
+      <c r="D17" s="3">
+        <v>9.189189189189189</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="F17" s="3">
+        <v>6.486486486486487</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.2167779657808363</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.14781180586459</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1464050470692909</v>
+      </c>
+      <c r="K17" s="4">
+        <v>87.17227431513192</v>
+      </c>
+      <c r="L17" s="4">
+        <v>89.22891347723561</v>
+      </c>
+      <c r="M17" s="5">
+        <v>185</v>
+      </c>
+      <c r="N17" s="5">
+        <v>2665826.070785522</v>
+      </c>
+      <c r="O17" s="4">
+        <v>101.0050418969243</v>
+      </c>
+      <c r="P17" s="5">
+        <v>26393</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2875,16 +4789,16 @@
         <v>1</v>
       </c>
       <c r="K3" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="M3" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N3" s="5">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -2922,13 +4836,13 @@
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -2966,13 +4880,13 @@
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -3007,10 +4921,10 @@
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L6" s="5">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
@@ -3051,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
         <v>10</v>
@@ -3095,16 +5009,16 @@
         <v>1</v>
       </c>
       <c r="K8" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8" s="5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M8" s="5">
         <v>2</v>
       </c>
       <c r="N8" s="5">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25" customHeight="1">
@@ -3139,16 +5053,16 @@
         <v>1</v>
       </c>
       <c r="K9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3183,16 +5097,16 @@
         <v>3</v>
       </c>
       <c r="K10" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L10" s="5">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M10" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -3227,16 +5141,16 @@
         <v>5</v>
       </c>
       <c r="K11" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
       </c>
       <c r="N11" s="5">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25" customHeight="1">
@@ -3274,13 +5188,13 @@
         <v>0</v>
       </c>
       <c r="L12" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -3315,16 +5229,16 @@
         <v>2</v>
       </c>
       <c r="K13" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L13" s="5">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M13" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25" customHeight="1">
@@ -3359,16 +5273,16 @@
         <v>2</v>
       </c>
       <c r="K14" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="5">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M14" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N14" s="5">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -3403,10 +5317,10 @@
         <v>0</v>
       </c>
       <c r="K15" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M15" s="5">
         <v>0</v>
@@ -3447,16 +5361,16 @@
         <v>4</v>
       </c>
       <c r="K16" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L16" s="5">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="M16" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N16" s="5">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3491,16 +5405,16 @@
         <v>1</v>
       </c>
       <c r="K17" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M17" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3516,9 +5430,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>142</v>
+      </c>
+      <c r="C3" s="5">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5">
+        <v>35</v>
+      </c>
+      <c r="E3" s="5">
+        <v>11</v>
+      </c>
+      <c r="F3" s="5">
+        <v>24</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>11</v>
+      </c>
+      <c r="I3" s="5">
+        <v>11</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>21</v>
+      </c>
+      <c r="M3" s="5">
+        <v>5</v>
+      </c>
+      <c r="N3" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>159</v>
+      </c>
+      <c r="C4" s="5">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5">
+        <v>21</v>
+      </c>
+      <c r="E4" s="5">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5">
+        <v>17</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>15</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>160</v>
+      </c>
+      <c r="C5" s="5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5">
+        <v>22</v>
+      </c>
+      <c r="E5" s="5">
+        <v>6</v>
+      </c>
+      <c r="F5" s="5">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>6</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>11</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>151</v>
+      </c>
+      <c r="C6" s="5">
+        <v>4</v>
+      </c>
+      <c r="D6" s="5">
+        <v>30</v>
+      </c>
+      <c r="E6" s="5">
+        <v>6</v>
+      </c>
+      <c r="F6" s="5">
+        <v>24</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>6</v>
+      </c>
+      <c r="I6" s="5">
+        <v>6</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>1</v>
+      </c>
+      <c r="L6" s="5">
+        <v>16</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>167</v>
+      </c>
+      <c r="C7" s="5">
+        <v>4</v>
+      </c>
+      <c r="D7" s="5">
+        <v>14</v>
+      </c>
+      <c r="E7" s="5">
+        <v>3</v>
+      </c>
+      <c r="F7" s="5">
+        <v>11</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>3</v>
+      </c>
+      <c r="I7" s="5">
+        <v>3</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>10</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>151</v>
+      </c>
+      <c r="C8" s="5">
+        <v>8</v>
+      </c>
+      <c r="D8" s="5">
+        <v>26</v>
+      </c>
+      <c r="E8" s="5">
+        <v>3</v>
+      </c>
+      <c r="F8" s="5">
+        <v>23</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5">
+        <v>3</v>
+      </c>
+      <c r="J8" s="5">
+        <v>1</v>
+      </c>
+      <c r="K8" s="5">
+        <v>2</v>
+      </c>
+      <c r="L8" s="5">
+        <v>16</v>
+      </c>
+      <c r="M8" s="5">
+        <v>2</v>
+      </c>
+      <c r="N8" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>128</v>
+      </c>
+      <c r="C9" s="5">
+        <v>9</v>
+      </c>
+      <c r="D9" s="5">
+        <v>48</v>
+      </c>
+      <c r="E9" s="5">
+        <v>3</v>
+      </c>
+      <c r="F9" s="5">
+        <v>45</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>3</v>
+      </c>
+      <c r="I9" s="5">
+        <v>3</v>
+      </c>
+      <c r="J9" s="5">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>34</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>151</v>
+      </c>
+      <c r="C10" s="5">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5">
+        <v>30</v>
+      </c>
+      <c r="E10" s="5">
+        <v>10</v>
+      </c>
+      <c r="F10" s="5">
+        <v>20</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>10</v>
+      </c>
+      <c r="I10" s="5">
+        <v>8</v>
+      </c>
+      <c r="J10" s="5">
+        <v>3</v>
+      </c>
+      <c r="K10" s="5">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5">
+        <v>15</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>154</v>
+      </c>
+      <c r="C11" s="5">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5">
+        <v>27</v>
+      </c>
+      <c r="E11" s="5">
+        <v>10</v>
+      </c>
+      <c r="F11" s="5">
+        <v>17</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>10</v>
+      </c>
+      <c r="I11" s="5">
+        <v>9</v>
+      </c>
+      <c r="J11" s="5">
+        <v>5</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>11</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>176</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>8</v>
+      </c>
+      <c r="E12" s="5">
+        <v>3</v>
+      </c>
+      <c r="F12" s="5">
+        <v>5</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>3</v>
+      </c>
+      <c r="I12" s="5">
+        <v>3</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>5</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>160</v>
+      </c>
+      <c r="C13" s="5">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5">
+        <v>22</v>
+      </c>
+      <c r="E13" s="5">
+        <v>8</v>
+      </c>
+      <c r="F13" s="5">
+        <v>14</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>8</v>
+      </c>
+      <c r="I13" s="5">
+        <v>8</v>
+      </c>
+      <c r="J13" s="5">
+        <v>2</v>
+      </c>
+      <c r="K13" s="5">
+        <v>2</v>
+      </c>
+      <c r="L13" s="5">
+        <v>12</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>129</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5">
+        <v>53</v>
+      </c>
+      <c r="E14" s="5">
+        <v>6</v>
+      </c>
+      <c r="F14" s="5">
+        <v>46</v>
+      </c>
+      <c r="G14" s="5">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5">
+        <v>6</v>
+      </c>
+      <c r="I14" s="5">
+        <v>5</v>
+      </c>
+      <c r="J14" s="5">
+        <v>2</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>37</v>
+      </c>
+      <c r="M14" s="5">
+        <v>1</v>
+      </c>
+      <c r="N14" s="5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>167</v>
+      </c>
+      <c r="C15" s="5">
+        <v>3</v>
+      </c>
+      <c r="D15" s="5">
+        <v>15</v>
+      </c>
+      <c r="E15" s="5">
+        <v>5</v>
+      </c>
+      <c r="F15" s="5">
+        <v>10</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>5</v>
+      </c>
+      <c r="I15" s="5">
+        <v>5</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>8</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>87</v>
+      </c>
+      <c r="C16" s="5">
+        <v>9</v>
+      </c>
+      <c r="D16" s="5">
+        <v>89</v>
+      </c>
+      <c r="E16" s="5">
+        <v>14</v>
+      </c>
+      <c r="F16" s="5">
+        <v>75</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>14</v>
+      </c>
+      <c r="I16" s="5">
+        <v>13</v>
+      </c>
+      <c r="J16" s="5">
+        <v>4</v>
+      </c>
+      <c r="K16" s="5">
+        <v>1</v>
+      </c>
+      <c r="L16" s="5">
+        <v>58</v>
+      </c>
+      <c r="M16" s="5">
+        <v>1</v>
+      </c>
+      <c r="N16" s="5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>165</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3</v>
+      </c>
+      <c r="D17" s="5">
+        <v>17</v>
+      </c>
+      <c r="E17" s="5">
+        <v>5</v>
+      </c>
+      <c r="F17" s="5">
+        <v>12</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>5</v>
+      </c>
+      <c r="I17" s="5">
+        <v>5</v>
+      </c>
+      <c r="J17" s="5">
+        <v>1</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>9</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3529,9 +6198,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3565,8 +6240,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3588,10 +6271,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4829392747722551</v>
@@ -3629,10 +6330,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.03627585203014076</v>
+      </c>
+      <c r="O3" s="5">
+        <v>69</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4862231745269202</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2314397133626717</v>
+      </c>
+      <c r="R3" s="5">
+        <v>69</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4769582379943738</v>
@@ -3670,9 +6389,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.2074145493491378</v>
+      </c>
+      <c r="O4" s="5">
+        <v>73</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.456185161206808</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2739124196403488</v>
+      </c>
+      <c r="R4" s="5">
+        <v>73</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3683,14 +6420,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3701,9 +6439,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3737,8 +6481,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3760,10 +6512,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3575573058322293</v>
@@ -3801,10 +6571,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1139517303891612</v>
+      </c>
+      <c r="O3" s="5">
+        <v>79</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3335707690384183</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2762536601435882</v>
+      </c>
+      <c r="R3" s="5">
+        <v>79</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4278742574408062</v>
@@ -3842,9 +6630,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.3085719225673129</v>
+      </c>
+      <c r="O4" s="5">
+        <v>80</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3397581281659449</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2993780128498112</v>
+      </c>
+      <c r="R4" s="5">
+        <v>80</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3855,14 +6661,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3873,9 +6680,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3909,8 +6722,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3932,10 +6753,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2198027866399278</v>
@@ -3973,10 +6812,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.08271918499933335</v>
+      </c>
+      <c r="O3" s="5">
+        <v>81</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2102532754219286</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1546217121511695</v>
+      </c>
+      <c r="R3" s="5">
+        <v>81</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2892157962838574</v>
@@ -4014,9 +6871,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.02289392665851405</v>
+      </c>
+      <c r="O4" s="5">
+        <v>79</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2907648329965972</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2214600482899448</v>
+      </c>
+      <c r="R4" s="5">
+        <v>79</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4027,14 +6902,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4045,9 +6921,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4081,8 +6963,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4104,10 +6994,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3527563172359003</v>
@@ -4145,10 +7053,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.008256548652794307</v>
+      </c>
+      <c r="O3" s="5">
+        <v>74</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3541691713039147</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2012143636904374</v>
+      </c>
+      <c r="R3" s="5">
+        <v>74</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3228147938673104</v>
@@ -4186,9 +7112,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.113316502628877</v>
+      </c>
+      <c r="O4" s="5">
+        <v>77</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3240175166225365</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2605848143889894</v>
+      </c>
+      <c r="R4" s="5">
+        <v>77</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4199,14 +7143,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4217,9 +7162,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4253,8 +7204,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4276,10 +7235,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.1372850333277143</v>
@@ -4317,10 +7294,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.01135295494287584</v>
+      </c>
+      <c r="O3" s="5">
+        <v>87</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1357875103610992</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1015452212564569</v>
+      </c>
+      <c r="R3" s="5">
+        <v>87</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2195751636048832</v>
@@ -4358,9 +7353,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.0631027940683655</v>
+      </c>
+      <c r="O4" s="5">
+        <v>80</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.228071066778991</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1675211118351562</v>
+      </c>
+      <c r="R4" s="5">
+        <v>80</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4371,350 +7384,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3178805346572751</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2039623501230684</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2128451672061387</v>
-      </c>
-      <c r="E3" s="4">
-        <v>77.31364886380055</v>
-      </c>
-      <c r="F3" s="4">
-        <v>80.5345328192676</v>
-      </c>
-      <c r="G3" s="5">
-        <v>94</v>
-      </c>
-      <c r="H3" s="5">
-        <v>74</v>
-      </c>
-      <c r="I3" s="5">
-        <v>7</v>
-      </c>
-      <c r="J3" s="5">
-        <v>13</v>
-      </c>
-      <c r="K3" s="5">
-        <v>3</v>
-      </c>
-      <c r="L3" s="5">
-        <v>10</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.323340878702245</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2763823921008396</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.248522418847871</v>
-      </c>
-      <c r="E4" s="4">
-        <v>81.1930926216645</v>
-      </c>
-      <c r="F4" s="4">
-        <v>85.16655603903912</v>
-      </c>
-      <c r="G4" s="5">
-        <v>91</v>
-      </c>
-      <c r="H4" s="5">
-        <v>77</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>13</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>13</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4671728057005042</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3064880808598545</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2959700072024354</v>
-      </c>
-      <c r="E3" s="4">
-        <v>67.6555941525545</v>
-      </c>
-      <c r="F3" s="4">
-        <v>73.40961016707139</v>
-      </c>
-      <c r="G3" s="5">
-        <v>94</v>
-      </c>
-      <c r="H3" s="5">
-        <v>64</v>
-      </c>
-      <c r="I3" s="5">
-        <v>6</v>
-      </c>
-      <c r="J3" s="5">
-        <v>24</v>
-      </c>
-      <c r="K3" s="5">
-        <v>3</v>
-      </c>
-      <c r="L3" s="5">
-        <v>21</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.5205905138520734</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4169578796277298</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4311773345409519</v>
-      </c>
-      <c r="E4" s="4">
-        <v>69.5204455408538</v>
-      </c>
-      <c r="F4" s="4">
-        <v>76.00904688153028</v>
-      </c>
-      <c r="G4" s="5">
-        <v>91</v>
-      </c>
-      <c r="H4" s="5">
-        <v>64</v>
-      </c>
-      <c r="I4" s="5">
-        <v>3</v>
-      </c>
-      <c r="J4" s="5">
-        <v>24</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>24</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/BothraExtendedICOHP2024.xlsx
+++ b/public/downloads/BothraExtendedICOHP2024.xlsx
@@ -1554,16 +1554,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.0128715771693644</v>
+        <v>0.006884094373070582</v>
       </c>
       <c r="O3" s="5">
         <v>74</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3183905413976887</v>
+        <v>0.3181064115631778</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2039144355949794</v>
+        <v>0.203877161632022</v>
       </c>
       <c r="R3" s="5">
         <v>74</v>
@@ -1613,16 +1613,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.05405497786027094</v>
+        <v>0.0255996451354914</v>
       </c>
       <c r="O4" s="5">
         <v>77</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3245007575473345</v>
+        <v>0.3227084621277043</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2757063815536988</v>
+        <v>0.2750664133421764</v>
       </c>
       <c r="R4" s="5">
         <v>77</v>
@@ -1795,16 +1795,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.07589145981201662</v>
+        <v>0.1239114145575044</v>
       </c>
       <c r="O3" s="5">
         <v>64</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4568039540887596</v>
+        <v>0.4563548727664786</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2883660085741433</v>
+        <v>0.28470517321045</v>
       </c>
       <c r="R3" s="5">
         <v>64</v>
@@ -1854,13 +1854,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2919753643087848</v>
+        <v>0.2805535871789715</v>
       </c>
       <c r="O4" s="5">
         <v>64</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4620500737694364</v>
+        <v>0.4619245597350428</v>
       </c>
       <c r="Q4" s="4">
         <v>0.3474234947683748</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.01676470390487029</v>
+        <v>0.005863226948633837</v>
       </c>
       <c r="O3" s="5">
         <v>77</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2737031875391309</v>
+        <v>0.2746514984037127</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1686330126913733</v>
+        <v>0.1671458678029208</v>
       </c>
       <c r="R3" s="5">
         <v>77</v>
@@ -2095,13 +2095,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04699040926869867</v>
+        <v>0.04806760661710996</v>
       </c>
       <c r="O4" s="5">
         <v>74</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3352925139609041</v>
+        <v>0.3353517006283993</v>
       </c>
       <c r="Q4" s="4">
         <v>0.2011993050480707</v>
@@ -2277,16 +2277,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.03376189849194864</v>
+        <v>0.0318944811718751</v>
       </c>
       <c r="O3" s="5">
         <v>80</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2730668598281666</v>
+        <v>0.2730761600101814</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1951511686109794</v>
+        <v>0.1951154108918449</v>
       </c>
       <c r="R3" s="5">
         <v>80</v>
@@ -2336,16 +2336,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.117955163104485</v>
+        <v>0.1004973205493371</v>
       </c>
       <c r="O4" s="5">
         <v>74</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4489634952503799</v>
+        <v>0.4470924691864498</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2374027136852435</v>
+        <v>0.2369867905276083</v>
       </c>
       <c r="R4" s="5">
         <v>74</v>
@@ -2518,16 +2518,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05440567682134034</v>
+        <v>-0.0664323570019576</v>
       </c>
       <c r="O3" s="5">
         <v>89</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2000756801303786</v>
+        <v>0.1997840150423874</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1496151129318241</v>
+        <v>0.1491719309267478</v>
       </c>
       <c r="R3" s="5">
         <v>89</v>
@@ -2577,16 +2577,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.0131191042704746</v>
+        <v>-0.03986877715576043</v>
       </c>
       <c r="O4" s="5">
         <v>87</v>
       </c>
       <c r="P4" s="4">
-        <v>0.225860254331095</v>
+        <v>0.2202692406468916</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2103197163542654</v>
+        <v>0.2044716445696388</v>
       </c>
       <c r="R4" s="5">
         <v>87</v>
@@ -2759,16 +2759,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1795598035314893</v>
+        <v>-0.1902719665014558</v>
       </c>
       <c r="O3" s="5">
         <v>80</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2677656617853166</v>
+        <v>0.2672987831673868</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1592812552019645</v>
+        <v>0.1590004769001461</v>
       </c>
       <c r="R3" s="5">
         <v>80</v>
@@ -2818,16 +2818,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.0653595971840879</v>
+        <v>0.008713944445815969</v>
       </c>
       <c r="O4" s="5">
         <v>80</v>
       </c>
       <c r="P4" s="4">
-        <v>0.320612133806489</v>
+        <v>0.3173774562639494</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2233522430463858</v>
+        <v>0.219450572699218</v>
       </c>
       <c r="R4" s="5">
         <v>80</v>
@@ -3000,16 +3000,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1755645989607876</v>
+        <v>0.2281550042187774</v>
       </c>
       <c r="O3" s="5">
         <v>69</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4393403106561931</v>
+        <v>0.4400653031002231</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1507328744154132</v>
+        <v>0.1448609272040642</v>
       </c>
       <c r="R3" s="5">
         <v>69</v>
@@ -3059,16 +3059,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3364760903101248</v>
+        <v>0.3790217799836171</v>
       </c>
       <c r="O4" s="5">
         <v>61</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7578558374710435</v>
+        <v>0.7647126358949806</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2778677128712014</v>
+        <v>0.2747943887509005</v>
       </c>
       <c r="R4" s="5">
         <v>60</v>
@@ -3241,16 +3241,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3799980288902891</v>
+        <v>-0.4025309762268421</v>
       </c>
       <c r="O3" s="5">
         <v>85</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1643812198647925</v>
+        <v>0.1624195838438134</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09947329699392547</v>
+        <v>0.09703886483735394</v>
       </c>
       <c r="R3" s="5">
         <v>85</v>
@@ -3300,16 +3300,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2186939960312101</v>
+        <v>-0.2771937161157183</v>
       </c>
       <c r="O4" s="5">
         <v>82</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2249649526870856</v>
+        <v>0.2136837246180428</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1659009045009317</v>
+        <v>0.1551407650205744</v>
       </c>
       <c r="R4" s="5">
         <v>82</v>
@@ -3482,16 +3482,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3541591323731986</v>
+        <v>0.411356160630703</v>
       </c>
       <c r="O3" s="5">
         <v>49</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6119827170718913</v>
+        <v>0.6184551334462192</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2170270575513353</v>
+        <v>0.2111894774961216</v>
       </c>
       <c r="R3" s="5">
         <v>49</v>
@@ -3541,22 +3541,22 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.259357368629606</v>
+        <v>0.3627270555219724</v>
       </c>
       <c r="O4" s="5">
         <v>38</v>
       </c>
       <c r="P4" s="4">
-        <v>1.046046642690524</v>
+        <v>1.051299365414205</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3956478893497778</v>
+        <v>0.3199719162150065</v>
       </c>
       <c r="R4" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3723,16 +3723,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2280357003599367</v>
+        <v>-0.237293990546334</v>
       </c>
       <c r="O3" s="5">
         <v>83</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1938337337137283</v>
+        <v>0.1936135017285672</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1116429356729935</v>
+        <v>0.1115050619812013</v>
       </c>
       <c r="R3" s="5">
         <v>83</v>
@@ -3782,16 +3782,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2012602623284877</v>
+        <v>-0.2278060669623585</v>
       </c>
       <c r="O4" s="5">
         <v>82</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2404786011029039</v>
+        <v>0.2365539652925567</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1844217598390109</v>
+        <v>0.1816850179417884</v>
       </c>
       <c r="R4" s="5">
         <v>82</v>
@@ -3928,13 +3928,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4714477193262163</v>
+        <v>0.4661501956830172</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2532742736321817</v>
+        <v>0.2509389445777881</v>
       </c>
       <c r="J3" s="4">
-        <v>0.227121294426946</v>
+        <v>0.2330711903211029</v>
       </c>
       <c r="K3" s="4">
         <v>72.54624011766875</v>
@@ -3978,13 +3978,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.336614280825472</v>
+        <v>0.3345775994004206</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2878885545869708</v>
+        <v>0.286716675202584</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2787546311755784</v>
+        <v>0.2774735758764654</v>
       </c>
       <c r="K4" s="4">
         <v>76.56315499172628</v>
@@ -4028,13 +4028,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.2498562577964954</v>
+        <v>0.2486806572585309</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1876231406196898</v>
+        <v>0.1863356587777833</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2006485138323065</v>
+        <v>0.1994975356788572</v>
       </c>
       <c r="K5" s="4">
         <v>81.82404853833467</v>
@@ -4078,13 +4078,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.3393378168390205</v>
+        <v>0.3355696072505813</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2314893617287718</v>
+        <v>0.2286331600928721</v>
       </c>
       <c r="J6" s="4">
-        <v>0.2236576443083025</v>
+        <v>0.2220756923643389</v>
       </c>
       <c r="K6" s="4">
         <v>76.74793160507436</v>
@@ -4128,13 +4128,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.1811810435180082</v>
+        <v>0.1767846954885979</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1331504383001452</v>
+        <v>0.1297167973273765</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1392259367113816</v>
+        <v>0.1355106458246423</v>
       </c>
       <c r="K7" s="4">
         <v>87.69277440705994</v>
@@ -4178,13 +4178,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.3213961071794064</v>
+        <v>0.3203701229219449</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2405235736004191</v>
+        <v>0.24017896548422</v>
       </c>
       <c r="J8" s="4">
-        <v>0.2266087230501719</v>
+        <v>0.2282413553384735</v>
       </c>
       <c r="K8" s="4">
         <v>79.22191579334412</v>
@@ -4228,13 +4228,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.4593844778235791</v>
+        <v>0.4590945566266913</v>
       </c>
       <c r="I9" s="4">
-        <v>0.317894751671259</v>
+        <v>0.3160643339894124</v>
       </c>
       <c r="J9" s="4">
-        <v>0.3010122220021558</v>
+        <v>0.2981256413484346</v>
       </c>
       <c r="K9" s="4">
         <v>68.57289943004238</v>
@@ -4278,13 +4278,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.3039984778330841</v>
+        <v>0.3045094357142342</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1845926526542581</v>
+        <v>0.1838343072475637</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1669961765068811</v>
+        <v>0.1663732811634242</v>
       </c>
       <c r="K10" s="4">
         <v>81.13311270454138</v>
@@ -4328,13 +4328,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.3595889886034175</v>
+        <v>0.3586733715509404</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2154538591012102</v>
+        <v>0.2152354244830559</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2130428392098363</v>
+        <v>0.2130264521306618</v>
       </c>
       <c r="K11" s="4">
         <v>80.14726971869794</v>
@@ -4378,13 +4378,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2127589031155959</v>
+        <v>0.2098605314208192</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1796225021235991</v>
+        <v>0.1765075848297678</v>
       </c>
       <c r="J12" s="4">
-        <v>0.1811562158423017</v>
+        <v>0.1783881336677186</v>
       </c>
       <c r="K12" s="4">
         <v>87.31402831402767</v>
@@ -4428,13 +4428,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.293760412887623</v>
+        <v>0.2919320764202905</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1913167491241752</v>
+        <v>0.189225524799682</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1799984476468247</v>
+        <v>0.1787192495829213</v>
       </c>
       <c r="K13" s="4">
         <v>79.07979407979391</v>
@@ -4478,13 +4478,13 @@
         <v>0.5405405405405406</v>
       </c>
       <c r="H14" s="4">
-        <v>0.5960155157380923</v>
+        <v>0.599756693826293</v>
       </c>
       <c r="I14" s="4">
-        <v>0.2098653574181054</v>
+        <v>0.2052950953653834</v>
       </c>
       <c r="J14" s="4">
-        <v>0.3317530713663741</v>
+        <v>0.3283840229041013</v>
       </c>
       <c r="K14" s="4">
         <v>64.01746644603791</v>
@@ -4528,13 +4528,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1941818668206231</v>
+        <v>0.1876359990354614</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1320904455901801</v>
+        <v>0.125567941574025</v>
       </c>
       <c r="J15" s="4">
-        <v>0.1357641601218892</v>
+        <v>0.1299340249796655</v>
       </c>
       <c r="K15" s="4">
         <v>89.93436293436262</v>
@@ -4560,13 +4560,13 @@
         <v>30</v>
       </c>
       <c r="B16" s="3">
-        <v>47.02702702702703</v>
+        <v>46.48648648648649</v>
       </c>
       <c r="C16" s="3">
         <v>4.864864864864865</v>
       </c>
       <c r="D16" s="3">
-        <v>48.10810810810811</v>
+        <v>48.64864864864865</v>
       </c>
       <c r="E16" s="3">
         <v>7.567567567567568</v>
@@ -4575,16 +4575,16 @@
         <v>40.54054054054054</v>
       </c>
       <c r="G16" s="3">
-        <v>0</v>
+        <v>0.5405405405405406</v>
       </c>
       <c r="H16" s="4">
-        <v>0.8254952426464617</v>
+        <v>0.8313677016034448</v>
       </c>
       <c r="I16" s="4">
-        <v>0.2950453519000804</v>
+        <v>0.2579912243868046</v>
       </c>
       <c r="J16" s="4">
-        <v>0.4165033535760633</v>
+        <v>0.4021090098165839</v>
       </c>
       <c r="K16" s="4">
         <v>50.09395109395107</v>
@@ -4628,13 +4628,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.2167779657808363</v>
+        <v>0.2147355675897729</v>
       </c>
       <c r="I17" s="4">
-        <v>0.14781180586459</v>
+        <v>0.146382373428281</v>
       </c>
       <c r="J17" s="4">
-        <v>0.1464050470692909</v>
+        <v>0.1444122575133366</v>
       </c>
       <c r="K17" s="4">
         <v>87.17227431513192</v>
@@ -6089,13 +6089,13 @@
         <v>30</v>
       </c>
       <c r="B16" s="5">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C16" s="5">
         <v>9</v>
       </c>
       <c r="D16" s="5">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E16" s="5">
         <v>14</v>
@@ -6104,7 +6104,7 @@
         <v>75</v>
       </c>
       <c r="G16" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="5">
         <v>14</v>
@@ -6331,16 +6331,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.03627585203014076</v>
+        <v>0.003179220065334221</v>
       </c>
       <c r="O3" s="5">
         <v>69</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4862231745269202</v>
+        <v>0.4831422037125955</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2314397133626717</v>
+        <v>0.2308464583723536</v>
       </c>
       <c r="R3" s="5">
         <v>69</v>
@@ -6390,16 +6390,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2074145493491378</v>
+        <v>0.1407898016735771</v>
       </c>
       <c r="O4" s="5">
         <v>73</v>
       </c>
       <c r="P4" s="4">
-        <v>0.456185161206808</v>
+        <v>0.4485980115645518</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2739124196403488</v>
+        <v>0.2699304726349795</v>
       </c>
       <c r="R4" s="5">
         <v>73</v>
@@ -6572,16 +6572,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1139517303891612</v>
+        <v>0.1689109781445239</v>
       </c>
       <c r="O3" s="5">
         <v>79</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3335707690384183</v>
+        <v>0.3299887230492335</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2762536601435882</v>
+        <v>0.2740785388813441</v>
       </c>
       <c r="R3" s="5">
         <v>79</v>
@@ -6631,16 +6631,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3085719225673129</v>
+        <v>0.2829924243164186</v>
       </c>
       <c r="O4" s="5">
         <v>80</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3397581281659449</v>
+        <v>0.3393177573895589</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2993780128498112</v>
+        <v>0.2991968348198084</v>
       </c>
       <c r="R4" s="5">
         <v>80</v>
@@ -6813,16 +6813,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.08271918499933335</v>
+        <v>-0.0712301801809474</v>
       </c>
       <c r="O3" s="5">
         <v>81</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2102532754219286</v>
+        <v>0.2097209329689143</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1546217121511695</v>
+        <v>0.1541457715861698</v>
       </c>
       <c r="R3" s="5">
         <v>81</v>
@@ -6872,16 +6872,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.02289392665851405</v>
+        <v>-0.008831885964724506</v>
       </c>
       <c r="O4" s="5">
         <v>79</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2907648329965972</v>
+        <v>0.2889247680631898</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2214600482899448</v>
+        <v>0.219340479822349</v>
       </c>
       <c r="R4" s="5">
         <v>79</v>
@@ -7054,16 +7054,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.008256548652794307</v>
+        <v>-0.004108391192026772</v>
       </c>
       <c r="O3" s="5">
         <v>74</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3541691713039147</v>
+        <v>0.3521963224273806</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2012143636904374</v>
+        <v>0.2004728597838375</v>
       </c>
       <c r="R3" s="5">
         <v>74</v>
@@ -7113,16 +7113,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.113316502628877</v>
+        <v>0.04568859186159102</v>
       </c>
       <c r="O4" s="5">
         <v>77</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3240175166225365</v>
+        <v>0.3183947586064151</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2605848143889894</v>
+        <v>0.2556963058444118</v>
       </c>
       <c r="R4" s="5">
         <v>77</v>
@@ -7295,16 +7295,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.01135295494287584</v>
+        <v>-0.02076180161989782</v>
       </c>
       <c r="O3" s="5">
         <v>87</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1357875103610992</v>
+        <v>0.1355042033018212</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1015452212564569</v>
+        <v>0.1011309717133631</v>
       </c>
       <c r="R3" s="5">
         <v>87</v>
@@ -7354,16 +7354,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.0631027940683655</v>
+        <v>0.01323975613525619</v>
       </c>
       <c r="O4" s="5">
         <v>80</v>
       </c>
       <c r="P4" s="4">
-        <v>0.228071066778991</v>
+        <v>0.2194260830221914</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1675211118351562</v>
+        <v>0.160803882682616</v>
       </c>
       <c r="R4" s="5">
         <v>80</v>
